--- a/docs/downloads/04/tbl_other_act_sex_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_marovoay_tous.xlsx
@@ -512,12 +512,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -535,12 +529,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -627,12 +615,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -696,12 +678,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15">
-        <v>0.9</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -719,12 +695,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -880,12 +850,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1087,12 +1051,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D32">
-        <v>2</v>
-      </c>
-      <c r="E32">
-        <v>0.9</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1225,12 +1183,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1294,12 +1246,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-      <c r="E41">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1455,12 +1401,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="D48">
-        <v>2</v>
-      </c>
-      <c r="E48">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1547,12 +1487,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="E52">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1616,12 +1550,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D55">
-        <v>2</v>
-      </c>
-      <c r="E55">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1777,12 +1705,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D62">
-        <v>2</v>
-      </c>
-      <c r="E62">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1892,12 +1814,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D67">
-        <v>3</v>
-      </c>
-      <c r="E67">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1961,12 +1877,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D70">
-        <v>4</v>
-      </c>
-      <c r="E70">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1983,12 +1893,6 @@
         <is>
           <t>Éleveur</t>
         </is>
-      </c>
-      <c r="D71">
-        <v>2</v>
-      </c>
-      <c r="E71">
-        <v>0.3</v>
       </c>
     </row>
     <row r="72">

--- a/docs/downloads/04/tbl_other_act_sex_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,14 +394,8 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>158</v>
-      </c>
-      <c r="E2">
-        <v>50.8</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -417,14 +411,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>2.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4">
@@ -440,14 +434,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="E4">
-        <v>2.9</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="5">
@@ -463,14 +457,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D5">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>28.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -486,14 +480,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>11.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -509,8 +503,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -526,8 +526,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>13</v>
+      </c>
+      <c r="E8">
+        <v>7.9</v>
       </c>
     </row>
     <row r="9">
@@ -538,19 +544,13 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>8</v>
-      </c>
-      <c r="E9">
-        <v>2.6</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -566,14 +566,8 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>152</v>
-      </c>
-      <c r="E10">
-        <v>65</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -589,14 +583,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="E11">
-        <v>2.1</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="12">
@@ -612,7 +606,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
@@ -629,14 +623,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D13">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E13">
-        <v>15.8</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="14">
@@ -659,7 +653,7 @@
         <v>20</v>
       </c>
       <c r="E14">
-        <v>8.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -675,48 +669,60 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>7</v>
+      </c>
+      <c r="E15">
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>15</v>
+      </c>
+      <c r="E16">
+        <v>11.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D17">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="E17">
-        <v>6.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="18">
@@ -732,14 +738,8 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>132</v>
-      </c>
-      <c r="E18">
-        <v>51.4</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -755,14 +755,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19">
-        <v>4.3</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="20">
@@ -778,14 +778,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E20">
-        <v>3.1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -801,14 +801,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D21">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="E21">
-        <v>25.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="22">
@@ -819,19 +819,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>27</v>
-      </c>
-      <c r="E22">
-        <v>10.5</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -842,13 +836,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>20</v>
+      </c>
+      <c r="E23">
+        <v>40.8</v>
       </c>
     </row>
     <row r="24">
@@ -859,19 +859,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D24">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E24">
-        <v>4.7</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="25">
@@ -887,14 +887,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D25">
-        <v>109</v>
+        <v>10</v>
       </c>
       <c r="E25">
-        <v>70.8</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="26">
@@ -910,83 +910,77 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26">
-        <v>3.9</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D27">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E27">
-        <v>13</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>10</v>
-      </c>
-      <c r="E28">
-        <v>6.5</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D29">
-        <v>9</v>
+        <v>103</v>
       </c>
       <c r="E29">
-        <v>5.8</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1002,14 +996,8 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>93</v>
-      </c>
-      <c r="E30">
-        <v>40.1</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1025,14 +1013,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E31">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="32">
@@ -1048,8 +1036,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>17</v>
+      </c>
+      <c r="E32">
+        <v>11</v>
       </c>
     </row>
     <row r="33">
@@ -1065,14 +1059,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D33">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="E33">
-        <v>44.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="34">
@@ -1083,19 +1077,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>17</v>
-      </c>
-      <c r="E34">
-        <v>7.3</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1106,19 +1094,13 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>7</v>
-      </c>
-      <c r="E35">
-        <v>3</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1134,14 +1116,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D36">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="E36">
-        <v>58.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="37">
@@ -1157,14 +1139,8 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>11</v>
-      </c>
-      <c r="E37">
-        <v>6.9</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1180,8 +1156,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>10</v>
+      </c>
+      <c r="E38">
+        <v>14.7</v>
       </c>
     </row>
     <row r="39">
@@ -1197,14 +1179,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D39">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="E39">
-        <v>20.8</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="40">
@@ -1220,54 +1202,54 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E40">
-        <v>6.3</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D42">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E42">
-        <v>6.3</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="43">
@@ -1283,14 +1265,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D43">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="E43">
-        <v>49.6</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="44">
@@ -1306,14 +1288,8 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
-      </c>
-      <c r="D44">
-        <v>15</v>
-      </c>
-      <c r="E44">
-        <v>6.1</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1329,14 +1305,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D45">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E45">
-        <v>8.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -1352,14 +1328,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D46">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="E46">
-        <v>24.4</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="47">
@@ -1375,14 +1351,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D47">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E47">
-        <v>7.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="48">
@@ -1393,13 +1369,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>9</v>
+      </c>
+      <c r="E48">
+        <v>16.7</v>
       </c>
     </row>
     <row r="49">
@@ -1410,19 +1392,13 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="D49">
-        <v>7</v>
-      </c>
-      <c r="E49">
-        <v>2.8</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -1438,14 +1414,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D50">
-        <v>142</v>
+        <v>11</v>
       </c>
       <c r="E50">
-        <v>77.59999999999999</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="51">
@@ -1461,14 +1437,8 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
-      </c>
-      <c r="D51">
-        <v>8</v>
-      </c>
-      <c r="E51">
-        <v>4.4</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1484,8 +1454,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="D52">
+        <v>11</v>
+      </c>
+      <c r="E52">
+        <v>20.4</v>
       </c>
     </row>
     <row r="53">
@@ -1501,14 +1477,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D53">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E53">
-        <v>6</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="54">
@@ -1524,54 +1500,60 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D54">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E54">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="D55">
+        <v>16</v>
+      </c>
+      <c r="E55">
+        <v>2.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D56">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="E56">
-        <v>6</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="57">
@@ -1587,14 +1569,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D57">
-        <v>505</v>
+        <v>317</v>
       </c>
       <c r="E57">
-        <v>48.3</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="58">
@@ -1610,14 +1592,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D58">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E58">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="59">
@@ -1633,14 +1615,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D59">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E59">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="60">
@@ -1656,14 +1638,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D60">
-        <v>317</v>
+        <v>99</v>
       </c>
       <c r="E60">
-        <v>30.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="61">
@@ -1679,14 +1661,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D61">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="E61">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="62">
@@ -1697,13 +1679,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="D62">
+        <v>14</v>
+      </c>
+      <c r="E62">
+        <v>5.4</v>
       </c>
     </row>
     <row r="63">
@@ -1714,19 +1702,13 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-      <c r="D63">
-        <v>5</v>
-      </c>
-      <c r="E63">
-        <v>0.5</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -1737,19 +1719,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D64">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="E64">
-        <v>3.3</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="65">
@@ -1765,14 +1747,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D65">
-        <v>496</v>
+        <v>8</v>
       </c>
       <c r="E65">
-        <v>67.90000000000001</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="66">
@@ -1788,14 +1770,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D66">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E66">
-        <v>4.1</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="67">
@@ -1811,8 +1793,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D67">
+        <v>48</v>
+      </c>
+      <c r="E67">
+        <v>18.6</v>
       </c>
     </row>
     <row r="68">
@@ -1828,94 +1816,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D68">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="E68">
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D69">
-        <v>48</v>
-      </c>
-      <c r="E69">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Pêcheur exploitant</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="D72">
-        <v>46</v>
-      </c>
-      <c r="E72">
-        <v>6.3</v>
+        <v>14.3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_other_act_sex_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_marovoay_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -401,7 +401,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -424,7 +424,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -447,7 +447,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -516,7 +516,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -556,7 +556,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -682,7 +682,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -728,7 +728,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -768,7 +768,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -791,7 +791,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -814,7 +814,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -854,7 +854,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -923,7 +923,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1049,7 +1049,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1089,7 +1089,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1146,7 +1146,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1192,7 +1192,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1232,7 +1232,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1278,7 +1278,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1318,7 +1318,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1341,7 +1341,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1404,7 +1404,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1467,7 +1467,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1513,7 +1513,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1536,7 +1536,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1559,7 +1559,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1582,7 +1582,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1651,7 +1651,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1674,7 +1674,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1697,7 +1697,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1714,7 +1714,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1737,7 +1737,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1760,7 +1760,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1783,7 +1783,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1806,7 +1806,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">

--- a/docs/downloads/04/tbl_other_act_sex_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -503,14 +503,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
@@ -526,14 +526,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D8">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E8">
-        <v>7.9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -544,12 +544,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
@@ -583,14 +583,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>37</v>
-      </c>
-      <c r="E11">
-        <v>42.5</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -606,8 +600,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>37</v>
+      </c>
+      <c r="E12">
+        <v>42.5</v>
       </c>
     </row>
     <row r="13">
@@ -623,14 +623,8 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>16</v>
-      </c>
-      <c r="E13">
-        <v>18.4</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -646,14 +640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="15">
@@ -669,60 +663,54 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bepako</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D16">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E16">
-        <v>11.1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bepako</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>66</v>
-      </c>
-      <c r="E17">
-        <v>48.9</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -738,8 +726,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>15</v>
+      </c>
+      <c r="E18">
+        <v>11.1</v>
       </c>
     </row>
     <row r="19">
@@ -755,14 +749,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D19">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="E19">
-        <v>8.9</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="20">
@@ -778,14 +772,8 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>27</v>
-      </c>
-      <c r="E20">
-        <v>20</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -801,14 +789,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D21">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="22">
@@ -819,13 +807,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
+          <t>Inactif / Retraité</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>12</v>
+      </c>
+      <c r="E22">
+        <v>8.9</v>
       </c>
     </row>
     <row r="23">
@@ -836,19 +830,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D23">
+        <v>27</v>
+      </c>
+      <c r="E23">
         <v>20</v>
-      </c>
-      <c r="E23">
-        <v>40.8</v>
       </c>
     </row>
     <row r="24">
@@ -859,19 +853,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>9</v>
-      </c>
-      <c r="E24">
-        <v>18.4</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -887,14 +875,8 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>10</v>
-      </c>
-      <c r="E25">
-        <v>20.4</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -910,93 +892,99 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D26">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E26">
-        <v>18.4</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Madiromiongana</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D27">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E27">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Madiromiongana</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
+          <t>Inactif / Retraité</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>6</v>
+      </c>
+      <c r="E28">
+        <v>12.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Madiromiongana</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D29">
-        <v>103</v>
+        <v>10</v>
       </c>
       <c r="E29">
-        <v>66.90000000000001</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Madiromiongana</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -1013,14 +1001,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E31">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="32">
@@ -1036,14 +1024,8 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>17</v>
-      </c>
-      <c r="E32">
-        <v>11</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1059,14 +1041,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D33">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="E33">
-        <v>7.1</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1077,12 +1059,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
@@ -1094,13 +1076,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>7</v>
+      </c>
+      <c r="E35">
+        <v>4.5</v>
       </c>
     </row>
     <row r="36">
@@ -1111,19 +1099,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
       <c r="D36">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="E36">
-        <v>48.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="37">
@@ -1134,13 +1122,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>17</v>
+      </c>
+      <c r="E37">
+        <v>11</v>
       </c>
     </row>
     <row r="38">
@@ -1151,19 +1145,13 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
-        </is>
-      </c>
-      <c r="D38">
-        <v>10</v>
-      </c>
-      <c r="E38">
-        <v>14.7</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1179,14 +1167,8 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D39">
-        <v>10</v>
-      </c>
-      <c r="E39">
-        <v>14.7</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1202,117 +1184,117 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>11</v>
-      </c>
-      <c r="E40">
-        <v>16.2</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Maroala</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>33</v>
+      </c>
+      <c r="E41">
+        <v>48.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Maroala</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
-      </c>
-      <c r="D42">
-        <v>31</v>
-      </c>
-      <c r="E42">
-        <v>22.1</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Maroala</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D43">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E43">
-        <v>42.9</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Maroala</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Inactif / Retraité</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>11</v>
+      </c>
+      <c r="E44">
+        <v>16.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Maroala</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D45">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="46">
@@ -1328,14 +1310,8 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>19</v>
-      </c>
-      <c r="E46">
-        <v>13.6</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -1351,14 +1327,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D47">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E47">
-        <v>14.3</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="48">
@@ -1369,19 +1345,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D48">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="E48">
-        <v>16.7</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="49">
@@ -1392,12 +1368,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
@@ -1409,19 +1385,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D50">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E50">
-        <v>20.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -1432,13 +1408,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Inactif / Retraité</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>15</v>
+      </c>
+      <c r="E51">
+        <v>10.7</v>
       </c>
     </row>
     <row r="52">
@@ -1449,19 +1431,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D52">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E52">
-        <v>20.4</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="53">
@@ -1472,19 +1454,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D53">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E53">
-        <v>14.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="54">
@@ -1500,140 +1482,128 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D54">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E54">
-        <v>18.5</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
-      </c>
-      <c r="D55">
-        <v>16</v>
-      </c>
-      <c r="E55">
-        <v>2.7</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D56">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="E56">
-        <v>10.1</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D57">
-        <v>317</v>
-      </c>
-      <c r="E57">
-        <v>53.5</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D58">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E58">
-        <v>1.7</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
       <c r="D59">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E59">
-        <v>5.7</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1642,33 +1612,27 @@
         </is>
       </c>
       <c r="D60">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="E60">
-        <v>16.7</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
           <t>Services &amp; Autres</t>
         </is>
-      </c>
-      <c r="D61">
-        <v>57</v>
-      </c>
-      <c r="E61">
-        <v>9.6</v>
       </c>
     </row>
     <row r="62">
@@ -1679,7 +1643,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1688,10 +1652,10 @@
         </is>
       </c>
       <c r="D62">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E62">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="63">
@@ -1702,13 +1666,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
           <t>Commerce &amp; Restauration</t>
         </is>
+      </c>
+      <c r="D63">
+        <v>60</v>
+      </c>
+      <c r="E63">
+        <v>10.1</v>
       </c>
     </row>
     <row r="64">
@@ -1719,7 +1689,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1728,10 +1698,10 @@
         </is>
       </c>
       <c r="D64">
-        <v>101</v>
+        <v>317</v>
       </c>
       <c r="E64">
-        <v>39.1</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="65">
@@ -1742,7 +1712,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1751,10 +1721,10 @@
         </is>
       </c>
       <c r="D65">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E65">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="66">
@@ -1765,7 +1735,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1774,10 +1744,10 @@
         </is>
       </c>
       <c r="D66">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E66">
-        <v>17.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="67">
@@ -1788,19 +1758,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
       <c r="D67">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E67">
-        <v>18.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="68">
@@ -1811,19 +1781,220 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D68">
+        <v>99</v>
+      </c>
+      <c r="E68">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
           <t>Services &amp; Autres</t>
         </is>
       </c>
-      <c r="D68">
-        <v>37</v>
-      </c>
-      <c r="E68">
-        <v>14.3</v>
+      <c r="D69">
+        <v>11</v>
+      </c>
+      <c r="E69">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="D70">
+        <v>14</v>
+      </c>
+      <c r="E70">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D72">
+        <v>101</v>
+      </c>
+      <c r="E72">
+        <v>39.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D73">
+        <v>8</v>
+      </c>
+      <c r="E73">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="D74">
+        <v>46</v>
+      </c>
+      <c r="E74">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Inactif / Retraité</t>
+        </is>
+      </c>
+      <c r="D75">
+        <v>30</v>
+      </c>
+      <c r="E75">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D76">
+        <v>48</v>
+      </c>
+      <c r="E76">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D77">
+        <v>7</v>
+      </c>
+      <c r="E77">
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>
